--- a/outputs/llm_eval/test_yjx/sig/NewsAuthor_correlation_results.xlsx
+++ b/outputs/llm_eval/test_yjx/sig/NewsAuthor_correlation_results.xlsx
@@ -417,13 +417,13 @@
         <v>4</v>
       </c>
       <c r="B2">
-        <v>0.1162245685679239</v>
+        <v>0.09775608784814459</v>
       </c>
       <c r="C2">
-        <v>0.1108195874697196</v>
+        <v>0.1038942827723291</v>
       </c>
       <c r="D2">
-        <v>0.1082532001982486</v>
+        <v>0.09436181046066229</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -431,13 +431,13 @@
         <v>5</v>
       </c>
       <c r="B3">
-        <v>0.3292121591424468</v>
+        <v>0.3230930725191511</v>
       </c>
       <c r="C3">
-        <v>0.3676040705861197</v>
+        <v>0.3697111965517147</v>
       </c>
       <c r="D3">
-        <v>0.2909568441934204</v>
+        <v>0.2995343849304283</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -445,13 +445,13 @@
         <v>6</v>
       </c>
       <c r="B4">
-        <v>0.2357642139428265</v>
+        <v>0.2942187035806119</v>
       </c>
       <c r="C4">
-        <v>0.2820407844495592</v>
+        <v>0.310342401485955</v>
       </c>
       <c r="D4">
-        <v>0.2032879978637296</v>
+        <v>0.2608103972070983</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -459,13 +459,13 @@
         <v>7</v>
       </c>
       <c r="B5">
-        <v>0.3336806743793179</v>
+        <v>0.3777160743397966</v>
       </c>
       <c r="C5">
-        <v>0.3337866689258943</v>
+        <v>0.3924827435797997</v>
       </c>
       <c r="D5">
-        <v>0.2827183558880333</v>
+        <v>0.3293145805876365</v>
       </c>
     </row>
   </sheetData>
